--- a/血常规报告汇总.xlsx
+++ b/血常规报告汇总.xlsx
@@ -1,39 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" tabRatio="600" autoFilterDateGrouping="true"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="汇总数据" sheetId="1" r:id="rId1" state="visible"/>
-    <sheet name="趋势图" sheetId="2" r:id="rId2" state="visible"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总数据" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="趋势图" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="true"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>2026-04-17</t>
-  </si>
-  <si>
-    <t>2026-04-27</t>
-  </si>
-  <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
-    <t>2026-05-13</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
   <fonts count="2">
     <font>
@@ -83,18 +66,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="false" pivotButton="false"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" quotePrefix="false" pivotButton="false" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="false" pivotButton="false" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="false"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -167,14 +150,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -197,7 +180,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="20000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="20000">
               <a:solidFill>
                 <a:srgbClr val="4472C4"/>
               </a:solidFill>
@@ -206,12 +189,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'趋势图'!$A$2:$A$25</f>
+              <f>'趋势图'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'趋势图'!$B$2:$B$25</f>
+              <f>'趋势图'!$B$2:$B$30</f>
             </numRef>
           </val>
         </ser>
@@ -227,8 +210,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -254,8 +237,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -278,14 +261,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -308,7 +291,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="20000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="20000">
               <a:solidFill>
                 <a:srgbClr val="ED7D31"/>
               </a:solidFill>
@@ -317,12 +300,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'趋势图'!$A$2:$A$25</f>
+              <f>'趋势图'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'趋势图'!$C$2:$C$25</f>
+              <f>'趋势图'!$C$2:$C$30</f>
             </numRef>
           </val>
         </ser>
@@ -338,8 +321,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -365,8 +348,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -389,14 +372,14 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -419,7 +402,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="20000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="20000">
               <a:solidFill>
                 <a:srgbClr val="7030A0"/>
               </a:solidFill>
@@ -428,12 +411,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'趋势图'!$A$2:$A$25</f>
+              <f>'趋势图'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'趋势图'!$D$2:$D$25</f>
+              <f>'趋势图'!$D$2:$D$30</f>
             </numRef>
           </val>
         </ser>
@@ -449,8 +432,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -476,8 +459,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -500,14 +483,14 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -530,7 +513,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="20000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="20000">
               <a:solidFill>
                 <a:srgbClr val="70AD47"/>
               </a:solidFill>
@@ -539,12 +522,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'趋势图'!$A$2:$A$25</f>
+              <f>'趋势图'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'趋势图'!$E$2:$E$25</f>
+              <f>'趋势图'!$E$2:$E$30</f>
             </numRef>
           </val>
         </ser>
@@ -560,8 +543,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -587,8 +570,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -611,14 +594,14 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -641,7 +624,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="20000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="20000">
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
@@ -650,12 +633,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'趋势图'!$A$2:$A$25</f>
+              <f>'趋势图'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'趋势图'!$F$2:$F$25</f>
+              <f>'趋势图'!$F$2:$F$30</f>
             </numRef>
           </val>
         </ser>
@@ -671,8 +654,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -698,8 +681,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -722,7 +705,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -737,9 +720,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -759,9 +742,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -781,9 +764,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -803,9 +786,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId4"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -825,9 +808,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId5"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -837,7 +820,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1120,20 +1103,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="true" summaryRight="true"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="14"/>
-    <col customWidth="true" max="2" min="2" width="18"/>
-    <col customWidth="true" max="3" min="3" width="22"/>
-    <col customWidth="true" max="4" min="4" width="20"/>
-    <col customWidth="true" max="5" min="5" width="16"/>
-    <col customWidth="true" max="6" min="6" width="18"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1697,83 +1680,113 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
         <v>4.92</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="2" t="n">
         <v>2.35</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="2" t="n">
         <v>1.71</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="2" t="n">
         <v>92</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="2" t="n">
         <v>88</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="s">
-        <v>1</v>
-      </c>
-      <c r="B27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
         <v>4.76</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="2" t="n">
         <v>2.89</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="2" t="n">
         <v>1.29</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="2" t="n">
         <v>139</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="2" t="n">
         <v>110</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="s">
-        <v>2</v>
-      </c>
-      <c r="B28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
         <v>5.41</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="2" t="n">
         <v>3.27</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="2" t="n">
         <v>1.51</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="2" t="n">
         <v>140</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="2" t="n">
         <v>110</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="s">
-        <v>3</v>
-      </c>
-      <c r="B29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
         <v>4.52</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="2" t="n">
         <v>2.24</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="2" t="n">
         <v>1.56</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="2" t="n">
         <v>121</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="2" t="n">
         <v>107</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -1787,7 +1800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2358,6 +2371,116 @@
         <v>83</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="E26" t="n">
+        <v>92</v>
+      </c>
+      <c r="F26" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E27" t="n">
+        <v>139</v>
+      </c>
+      <c r="F27" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="E28" t="n">
+        <v>140</v>
+      </c>
+      <c r="F28" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="E29" t="n">
+        <v>121</v>
+      </c>
+      <c r="F29" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E30" t="n">
+        <v>60</v>
+      </c>
+      <c r="F30" t="n">
+        <v>130</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/血常规报告汇总.xlsx
+++ b/血常规报告汇总.xlsx
@@ -189,12 +189,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'趋势图'!$A$2:$A$30</f>
+              <f>'趋势图'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'趋势图'!$B$2:$B$30</f>
+              <f>'趋势图'!$B$2:$B$33</f>
             </numRef>
           </val>
         </ser>
@@ -300,12 +300,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'趋势图'!$A$2:$A$30</f>
+              <f>'趋势图'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'趋势图'!$C$2:$C$30</f>
+              <f>'趋势图'!$C$2:$C$33</f>
             </numRef>
           </val>
         </ser>
@@ -411,12 +411,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'趋势图'!$A$2:$A$30</f>
+              <f>'趋势图'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'趋势图'!$D$2:$D$30</f>
+              <f>'趋势图'!$D$2:$D$33</f>
             </numRef>
           </val>
         </ser>
@@ -522,12 +522,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'趋势图'!$A$2:$A$30</f>
+              <f>'趋势图'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'趋势图'!$E$2:$E$30</f>
+              <f>'趋势图'!$E$2:$E$33</f>
             </numRef>
           </val>
         </ser>
@@ -633,12 +633,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'趋势图'!$A$2:$A$30</f>
+              <f>'趋势图'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'趋势图'!$F$2:$F$30</f>
+              <f>'趋势图'!$F$2:$F$33</f>
             </numRef>
           </val>
         </ser>
@@ -1108,7 +1108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1789,6 +1789,72 @@
         <v>130</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>128</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1800,7 +1866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2481,6 +2547,72 @@
         <v>130</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="C31" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="E31" t="n">
+        <v>49</v>
+      </c>
+      <c r="F31" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="E32" t="n">
+        <v>48</v>
+      </c>
+      <c r="F32" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E33" t="n">
+        <v>49</v>
+      </c>
+      <c r="F33" t="n">
+        <v>128</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
